--- a/testing_electricity_202604_highlighted.xlsx
+++ b/testing_electricity_202604_highlighted.xlsx
@@ -28287,7 +28287,7 @@
       <c r="H148" s="168" t="n">
         <v>335356</v>
       </c>
-      <c r="I148" s="304" t="n">
+      <c r="I148" s="168" t="n">
         <v>620519</v>
       </c>
       <c r="J148" s="168" t="n">
@@ -28342,7 +28342,7 @@
       <c r="AA148" s="168" t="n">
         <v>281582</v>
       </c>
-      <c r="AB148" s="168" t="n">
+      <c r="AB148" s="304" t="n">
         <v>665379</v>
       </c>
       <c r="AD148" s="168" t="n">

--- a/testing_electricity_202604_highlighted.xlsx
+++ b/testing_electricity_202604_highlighted.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7980" yWindow="780" windowWidth="21420" windowHeight="15280" tabRatio="887" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3240" yWindow="780" windowWidth="26160" windowHeight="16780" tabRatio="887" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLP Tariff" sheetId="1" state="visible" r:id="rId1"/>
@@ -14585,6 +14585,11 @@
           <t>Corner Stone EV Charger kWh</t>
         </is>
       </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>HELLOOOO</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="26" customHeight="1" s="279">
       <c r="A4" s="35" t="n">
@@ -28464,6 +28469,9 @@
       </c>
       <c r="AI149" s="168" t="n">
         <v>43012</v>
+      </c>
+      <c r="AJ149" s="4" t="n">
+        <v>10000000</v>
       </c>
     </row>
     <row r="150" ht="23.25" customHeight="1" s="279">

--- a/testing_electricity_202604_highlighted.xlsx
+++ b/testing_electricity_202604_highlighted.xlsx
@@ -27553,7 +27553,7 @@
       <c r="AH140" s="49" t="n">
         <v>14241.92</v>
       </c>
-      <c r="AI140" s="49" t="n">
+      <c r="AI140" s="304" t="n">
         <v>32039</v>
       </c>
     </row>
@@ -27653,7 +27653,7 @@
       <c r="AH141" s="49" t="n">
         <v>14634.33</v>
       </c>
-      <c r="AI141" s="49" t="n">
+      <c r="AI141" s="304" t="n">
         <v>41319</v>
       </c>
     </row>
